--- a/src/nodes/LPC/compressor_blade_strength.xlsx
+++ b/src/nodes/LPC/compressor_blade_strength.xlsx
@@ -1183,28 +1183,28 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>440.07443020668313</v>
+        <v>447.55974118793</v>
       </c>
       <c r="C3">
-        <v>279.75445114719196</v>
+        <v>223.60376715523046</v>
       </c>
       <c r="D3">
-        <v>12.948939590807969</v>
+        <v>9.3359472206941216</v>
       </c>
       <c r="E3">
-        <v>46.286804509126192</v>
+        <v>41.752191116766419</v>
       </c>
       <c r="F3">
-        <v>282.06518102315431</v>
+        <v>225.65214481852343</v>
       </c>
       <c r="G3">
         <v>27.222488222581564</v>
       </c>
       <c r="H3">
-        <v>13.299304169079845</v>
+        <v>10.002377889716048</v>
       </c>
       <c r="I3">
-        <v>47.149754963864616</v>
+        <v>44.326535862356977</v>
       </c>
       <c r="J3">
         <v>97.126137383957371</v>
@@ -1252,31 +1252,31 @@
         <v>50.195285369280967</v>
       </c>
       <c r="Y3">
-        <v>28.046871074079434</v>
+        <v>28.04687107407943</v>
       </c>
       <c r="Z3">
         <v>15.907903970049285</v>
       </c>
       <c r="AA3">
-        <v>2.012122971977619</v>
+        <v>2.0121229719776186</v>
       </c>
       <c r="AB3">
         <v>1.1638294233104705</v>
       </c>
       <c r="AC3">
-        <v>0.59273307729115166</v>
+        <v>0.5904351234124503</v>
       </c>
       <c r="AD3">
         <v>0.59864358983844579</v>
       </c>
       <c r="AE3">
-        <v>768.40385470714921</v>
+        <v>424.07219344880696</v>
       </c>
       <c r="AF3">
         <v>5.2965967193110952</v>
       </c>
       <c r="AG3">
-        <v>62002.777644461974</v>
+        <v>49602.201789388608</v>
       </c>
       <c r="AH3">
         <v>1924.7567159658063</v>
@@ -1297,136 +1297,136 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-6.3317760233163245</v>
+        <v>-6.33169794118726</v>
       </c>
       <c r="AO3">
         <v>-3.5916695882857015</v>
       </c>
       <c r="AP3">
-        <v>-1.9467251772619745</v>
+        <v>-1.9469791233585783</v>
       </c>
       <c r="AQ3">
         <v>-1.1263647390397329</v>
       </c>
       <c r="AR3">
-        <v>1840.0332349429518</v>
+        <v>1466.4373769992071</v>
       </c>
       <c r="AS3">
         <v>99.741512498921381</v>
       </c>
       <c r="AT3">
-        <v>-0.72830247451637709</v>
+        <v>-0.75218124417265164</v>
       </c>
       <c r="AU3">
-        <v>-0.15758439220180537</v>
+        <v>-0.28199312288744122</v>
       </c>
       <c r="AV3">
-        <v>-0.47229347200482524</v>
+        <v>-0.48777850387383581</v>
       </c>
       <c r="AW3">
-        <v>0.13584417907107932</v>
+        <v>0.24308958360087876</v>
       </c>
       <c r="AX3">
-        <v>3.779874422891353</v>
+        <v>3.9038047318386107</v>
       </c>
       <c r="AY3">
-        <v>3.5599516488885463E-05</v>
+        <v>6.3704397927479256E-05</v>
       </c>
       <c r="AZ3">
-        <v>-8.3645242094202974</v>
+        <v>-8.6387709048111248</v>
       </c>
       <c r="BA3">
-        <v>4.12513235092419E-05</v>
+        <v>7.3818157858643411E-05</v>
       </c>
       <c r="BB3">
-        <v>-0.0066596307373711092</v>
+        <v>-0.0091427131054823817</v>
       </c>
       <c r="BC3">
-        <v>-0.0037993766649034731</v>
+        <v>-0.00521599555605124</v>
       </c>
       <c r="BD3">
-        <v>-0.29081299781232312</v>
+        <v>-0.30033876249488395</v>
       </c>
       <c r="BE3">
-        <v>0.00048193397992651947</v>
+        <v>0.00086240815034237044</v>
       </c>
       <c r="BF3">
-        <v>-0.1580476875578497</v>
+        <v>-0.20480844746979354</v>
       </c>
       <c r="BG3">
-        <v>0.0048318294745302885</v>
+        <v>0.00864643144800613</v>
       </c>
       <c r="BH3">
-        <v>55.009274722373377</v>
+        <v>54.982372052837079</v>
       </c>
       <c r="BI3">
-        <v>45.528473159595251</v>
+        <v>44.90784731382449</v>
       </c>
       <c r="BJ3">
-        <v>-4.6850479775034319</v>
+        <v>-4.8348278729903615</v>
       </c>
       <c r="BK3">
-        <v>5.4376299509492385E-05</v>
+        <v>9.7231503735433755E-05</v>
       </c>
       <c r="BL3">
-        <v>-7.8932275623662012</v>
+        <v>-8.15429295332785</v>
       </c>
       <c r="BM3">
-        <v>3.4950417966798828E-06</v>
+        <v>7.3079016340228171E-06</v>
       </c>
       <c r="BN3">
-        <v>1.1961303333876798</v>
+        <v>0.82610770112185283</v>
       </c>
       <c r="BO3">
-        <v>0.01013412871735817</v>
+        <v>0.011850300964958642</v>
       </c>
       <c r="BP3">
-        <v>-2.4700865526155948</v>
+        <v>-1.8883456280940032</v>
       </c>
       <c r="BQ3">
-        <v>3.7261561804775174</v>
+        <v>3.0911333442600468</v>
       </c>
       <c r="BR3">
-        <v>32.1103241884666</v>
+        <v>33.994616427994139</v>
       </c>
       <c r="BS3">
-        <v>-3.1086426134664737</v>
+        <v>-2.8533696946271747</v>
       </c>
       <c r="BT3">
-        <v>-0.04810098304344048</v>
+        <v>-0.048074865834722563</v>
       </c>
       <c r="BU3">
-        <v>0.87194312704732946</v>
+        <v>0.87194456741801774</v>
       </c>
       <c r="BV3">
-        <v>19.302065246715564</v>
+        <v>19.302024232876111</v>
       </c>
       <c r="BW3">
-        <v>-1.3689906721087779</v>
+        <v>-1.3695688234802819</v>
       </c>
       <c r="BX3">
-        <v>-23.033262020104587</v>
+        <v>-35.552303529843734</v>
       </c>
       <c r="BY3">
-        <v>0.008951692146370498</v>
+        <v>0.016006778077740522</v>
       </c>
       <c r="BZ3">
-        <v>23.041542956810034</v>
+        <v>38.119641825735535</v>
       </c>
       <c r="CA3">
-        <v>-0.014089479185429929</v>
+        <v>-0.025214946213182574</v>
       </c>
       <c r="CB3">
-        <v>70.191475856121215</v>
+        <v>82.446432074873186</v>
       </c>
       <c r="CC3">
-        <v>0.010172480934085397</v>
+        <v>0.018192793111974422</v>
       </c>
       <c r="CD3">
-        <v>2.9918162773847197</v>
+        <v>2.5471084037850158</v>
       </c>
       <c r="CE3">
-        <v>20643.931540470465</v>
+        <v>11543.032381420249</v>
       </c>
     </row>
     <row r="4" spans="1:83">
@@ -1434,28 +1434,28 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>435.74359794931456</v>
+        <v>443.14615453651362</v>
       </c>
       <c r="C4">
-        <v>344.23764991529089</v>
+        <v>277.39590595340485</v>
       </c>
       <c r="D4">
-        <v>15.606887352283085</v>
+        <v>11.342523430887196</v>
       </c>
       <c r="E4">
-        <v>45.337537471928442</v>
+        <v>40.889296444023351</v>
       </c>
       <c r="F4">
-        <v>321.98096759425704</v>
+        <v>257.58477407540556</v>
       </c>
       <c r="G4">
         <v>43.9970296024267</v>
       </c>
       <c r="H4">
-        <v>15.427542710989449</v>
+        <v>11.551906367606513</v>
       </c>
       <c r="I4">
-        <v>47.914455398588665</v>
+        <v>44.847007782473973</v>
       </c>
       <c r="J4">
         <v>126.21894563199891</v>
@@ -1503,31 +1503,31 @@
         <v>61.220150588891464</v>
       </c>
       <c r="Y4">
-        <v>29.965724288101779</v>
+        <v>29.965724288101782</v>
       </c>
       <c r="Z4">
         <v>20.223705374486521</v>
       </c>
       <c r="AA4">
-        <v>5.6842107611099912</v>
+        <v>5.6842107611099921</v>
       </c>
       <c r="AB4">
         <v>2.7384195771576949</v>
       </c>
       <c r="AC4">
-        <v>1.5533774022818214</v>
+        <v>1.5473069434953228</v>
       </c>
       <c r="AD4">
         <v>1.1046778930124845</v>
       </c>
       <c r="AE4">
-        <v>1796.9415297431096</v>
+        <v>1189.5229163803306</v>
       </c>
       <c r="AF4">
         <v>35.192005183714564</v>
       </c>
       <c r="AG4">
-        <v>80842.334981569875</v>
+        <v>64673.686297790962</v>
       </c>
       <c r="AH4">
         <v>5028.9805803069057</v>
@@ -1548,136 +1548,136 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-6.8947026954433932</v>
+        <v>-6.8941200056745062</v>
       </c>
       <c r="AO4">
         <v>-4.6028246256487035</v>
       </c>
       <c r="AP4">
-        <v>-5.4993285604878759</v>
+        <v>-5.5000590198752093</v>
       </c>
       <c r="AQ4">
         <v>-2.650173947706997</v>
       </c>
       <c r="AR4">
-        <v>2244.0478506155291</v>
+        <v>1788.4981489578845</v>
       </c>
       <c r="AS4">
         <v>204.96062699815772</v>
       </c>
       <c r="AT4">
-        <v>-0.47147541238330848</v>
+        <v>-0.18669160624573961</v>
       </c>
       <c r="AU4">
-        <v>-0.66861720913796718</v>
+        <v>-0.074107818746819029</v>
       </c>
       <c r="AV4">
-        <v>-0.55067988458895056</v>
+        <v>-0.218054450944618</v>
       </c>
       <c r="AW4">
-        <v>0.33417769710979339</v>
+        <v>0.037039399925962321</v>
       </c>
       <c r="AX4">
-        <v>4.8142121104270981</v>
+        <v>1.906298755135563</v>
       </c>
       <c r="AY4">
-        <v>0.0056214437217648764</v>
+        <v>0.000623066422363102</v>
       </c>
       <c r="AZ4">
-        <v>-8.6766393387367469</v>
+        <v>-3.435716248224618</v>
       </c>
       <c r="BA4">
-        <v>0.011356231870604708</v>
+        <v>0.0012586956506827878</v>
       </c>
       <c r="BB4">
-        <v>0.044486320727360362</v>
+        <v>0.023577164757637166</v>
       </c>
       <c r="BC4">
-        <v>0.032620500703672978</v>
+        <v>0.017288152963538507</v>
       </c>
       <c r="BD4">
-        <v>-0.28995149489233346</v>
+        <v>-0.11480363170443142</v>
       </c>
       <c r="BE4">
-        <v>-0.019144823665202315</v>
+        <v>-0.0021219660858105508</v>
       </c>
       <c r="BF4">
-        <v>-0.12920914088922009</v>
+        <v>-0.0641899639489841</v>
       </c>
       <c r="BG4">
-        <v>-0.093407323863106628</v>
+        <v>-0.010353042517915521</v>
       </c>
       <c r="BH4">
-        <v>34.365983087824013</v>
+        <v>34.381593674572862</v>
       </c>
       <c r="BI4">
-        <v>46.959601175730533</v>
+        <v>35.350186988352569</v>
       </c>
       <c r="BJ4">
-        <v>-0.923878085559608</v>
+        <v>-0.36689677357378514</v>
       </c>
       <c r="BK4">
-        <v>0.012136672525177424</v>
+        <v>0.0012364387740720179</v>
       </c>
       <c r="BL4">
-        <v>-9.8796334821550786</v>
+        <v>-3.9119698157944915</v>
       </c>
       <c r="BM4">
-        <v>0.0036422262192938194</v>
+        <v>0.00066614237644471122</v>
       </c>
       <c r="BN4">
-        <v>13.370830262502684</v>
+        <v>11.095391543862641</v>
       </c>
       <c r="BO4">
-        <v>0.12032429641983808</v>
+        <v>0.21601259554214772</v>
       </c>
       <c r="BP4">
-        <v>-11.992418611292383</v>
+        <v>-10.43547844113241</v>
       </c>
       <c r="BQ4">
-        <v>6.036302535815909</v>
+        <v>5.0119612090662962</v>
       </c>
       <c r="BR4">
-        <v>31.535831916141831</v>
+        <v>32.064631082208471</v>
       </c>
       <c r="BS4">
-        <v>-13.911258056266725</v>
+        <v>-12.64481035496641</v>
       </c>
       <c r="BT4">
-        <v>0.31972415316779812</v>
+        <v>-0.030665757064667946</v>
       </c>
       <c r="BU4">
-        <v>1.159073248546769</v>
+        <v>1.1586523284196386</v>
       </c>
       <c r="BV4">
-        <v>19.265056237236994</v>
+        <v>19.260743155236135</v>
       </c>
       <c r="BW4">
-        <v>-2.5664806396569046</v>
+        <v>-2.5986511512056252</v>
       </c>
       <c r="BX4">
-        <v>-4.56907719002998</v>
+        <v>-2.1771099498754789</v>
       </c>
       <c r="BY4">
-        <v>0.39949821948286579</v>
+        <v>0.040712247206733096</v>
       </c>
       <c r="BZ4">
-        <v>11.006274907881954</v>
+        <v>5.83968815871933</v>
       </c>
       <c r="CA4">
-        <v>-0.89905526101283761</v>
+        <v>-0.0938525128860926</v>
       </c>
       <c r="CB4">
-        <v>58.920871979714747</v>
+        <v>50.686736586472541</v>
       </c>
       <c r="CC4">
-        <v>0.41027278184306515</v>
+        <v>0.042008005927440945</v>
       </c>
       <c r="CD4">
-        <v>3.5641020396354404</v>
+        <v>4.1430956921390267</v>
       </c>
       <c r="CE4">
-        <v>511.85457406318466</v>
+        <v>4999.0470950400777</v>
       </c>
     </row>
     <row r="5" spans="1:83">
@@ -1685,28 +1685,28 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>408.4214732278175</v>
+        <v>416.10101215926147</v>
       </c>
       <c r="C5">
-        <v>467.94214553216739</v>
+        <v>379.75914538217023</v>
       </c>
       <c r="D5">
-        <v>20.641008249861347</v>
+        <v>15.115239758429466</v>
       </c>
       <c r="E5">
-        <v>44.110171411013539</v>
+        <v>39.802174463022496</v>
       </c>
       <c r="F5">
-        <v>410.0602845013932</v>
+        <v>328.04822760111449</v>
       </c>
       <c r="G5">
         <v>90.690433622953591</v>
       </c>
       <c r="H5">
-        <v>19.759732473881819</v>
+        <v>14.73879577050991</v>
       </c>
       <c r="I5">
-        <v>48.18738419866331</v>
+        <v>44.928746843989458</v>
       </c>
       <c r="J5">
         <v>164.34965460071388</v>
@@ -1760,25 +1760,25 @@
         <v>29.035532188306806</v>
       </c>
       <c r="AA5">
-        <v>6.3759082313576521</v>
+        <v>6.3759082313576529</v>
       </c>
       <c r="AB5">
         <v>3.4244919662461504</v>
       </c>
       <c r="AC5">
-        <v>1.5441367809656457</v>
+        <v>1.5381031679748503</v>
       </c>
       <c r="AD5">
         <v>0.96318433789519375</v>
       </c>
       <c r="AE5">
-        <v>2897.0241312558155</v>
+        <v>1915.3253199800497</v>
       </c>
       <c r="AF5">
         <v>118.92825150172811</v>
       </c>
       <c r="AG5">
-        <v>131120.38103589966</v>
+        <v>104896.01363700451</v>
       </c>
       <c r="AH5">
         <v>21365.739884983082</v>
@@ -1799,136 +1799,136 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>-7.7787534495921395</v>
+        <v>-7.7781038202643868</v>
       </c>
       <c r="AO5">
         <v>-6.5904160101857636</v>
       </c>
       <c r="AP5">
-        <v>-6.1685341152695958</v>
+        <v>-6.1693532336846344</v>
       </c>
       <c r="AQ5">
         <v>-3.3141757110402787</v>
       </c>
       <c r="AR5">
-        <v>3225.2286598844903</v>
+        <v>2570.4944158188341</v>
       </c>
       <c r="AS5">
         <v>606.54941860941869</v>
       </c>
       <c r="AT5">
-        <v>-0.36836095670457447</v>
+        <v>-0.15973174228782433</v>
       </c>
       <c r="AU5">
-        <v>-0.91028251906719471</v>
+        <v>-0.34734464543353477</v>
       </c>
       <c r="AV5">
-        <v>-0.47186014600230131</v>
+        <v>-0.20461192171781209</v>
       </c>
       <c r="AW5">
-        <v>0.47628808530685895</v>
+        <v>0.18174150623551194</v>
       </c>
       <c r="AX5">
-        <v>4.9389103799388261</v>
+        <v>2.1416514036902874</v>
       </c>
       <c r="AY5">
-        <v>0.034338847498788148</v>
+        <v>0.01310298128243232</v>
       </c>
       <c r="AZ5">
-        <v>-9.4626322057741259</v>
+        <v>-4.1032652927693123</v>
       </c>
       <c r="BA5">
-        <v>0.066950294332991128</v>
+        <v>0.025546822837588721</v>
       </c>
       <c r="BB5">
-        <v>0.07343727120350256</v>
+        <v>0.04288643778025477</v>
       </c>
       <c r="BC5">
-        <v>0.051614490846002496</v>
+        <v>0.030139903449141286</v>
       </c>
       <c r="BD5">
-        <v>-0.33899876730016082</v>
+        <v>-0.14698944086910934</v>
       </c>
       <c r="BE5">
-        <v>-0.073312459802984536</v>
+        <v>-0.027974564513915147</v>
       </c>
       <c r="BF5">
-        <v>-0.10510844440787708</v>
+        <v>-0.057183334056100522</v>
       </c>
       <c r="BG5">
-        <v>-0.12086807365352262</v>
+        <v>-0.046120833118676326</v>
       </c>
       <c r="BH5">
-        <v>34.478880752803185</v>
+        <v>34.61920373918084</v>
       </c>
       <c r="BI5">
-        <v>50.616277639174911</v>
+        <v>49.659683754010643</v>
       </c>
       <c r="BJ5">
-        <v>-1.2855027960600349</v>
+        <v>-0.5686819932695959</v>
       </c>
       <c r="BK5">
-        <v>0.073535185899818445</v>
+        <v>0.02795402517622354</v>
       </c>
       <c r="BL5">
-        <v>-10.596307213559967</v>
+        <v>-4.5934798996299886</v>
       </c>
       <c r="BM5">
-        <v>0.015939723758532184</v>
+        <v>0.0065498665658146726</v>
       </c>
       <c r="BN5">
-        <v>10.321719624151791</v>
+        <v>8.38993930209719</v>
       </c>
       <c r="BO5">
-        <v>0.06913136222499168</v>
+        <v>0.074727006281017111</v>
       </c>
       <c r="BP5">
-        <v>-9.74243427787645</v>
+        <v>-8.7611202495967344</v>
       </c>
       <c r="BQ5">
-        <v>5.4671351541415252</v>
+        <v>4.5615198186248458</v>
       </c>
       <c r="BR5">
-        <v>32.239744601118396</v>
+        <v>32.633083344943543</v>
       </c>
       <c r="BS5">
-        <v>-12.177398350089476</v>
+        <v>-11.080254235534204</v>
       </c>
       <c r="BT5">
-        <v>0.31437481498420011</v>
+        <v>0.31448025929625217</v>
       </c>
       <c r="BU5">
-        <v>1.0796969756788846</v>
+        <v>1.0796662679270117</v>
       </c>
       <c r="BV5">
-        <v>19.278583893378926</v>
+        <v>19.27836661086387</v>
       </c>
       <c r="BW5">
-        <v>-2.2238911643515809</v>
+        <v>-2.225773946756433</v>
       </c>
       <c r="BX5">
-        <v>-3.2132647079451386</v>
+        <v>-1.738023831386982</v>
       </c>
       <c r="BY5">
-        <v>0.66735888061619808</v>
+        <v>0.25367860164579176</v>
       </c>
       <c r="BZ5">
-        <v>8.0089124932364477</v>
+        <v>4.7188828933027738</v>
       </c>
       <c r="CA5">
-        <v>-1.3894490826540757</v>
+        <v>-0.529076999766289</v>
       </c>
       <c r="CB5">
-        <v>56.196394988193937</v>
+        <v>49.6476626686993</v>
       </c>
       <c r="CC5">
-        <v>0.67821601777458651</v>
+        <v>0.25783708845029474</v>
       </c>
       <c r="CD5">
-        <v>3.7368945115450556</v>
+        <v>4.2298063737932194</v>
       </c>
       <c r="CE5">
-        <v>309.63586010408278</v>
+        <v>814.46777599834456</v>
       </c>
     </row>
   </sheetData>
@@ -2780,28 +2780,28 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>440.07443020668313</v>
+        <v>447.55974118793</v>
       </c>
       <c r="C3">
-        <v>143.00704677873924</v>
+        <v>95.338031185826168</v>
       </c>
       <c r="D3">
-        <v>5.5303497566457178</v>
+        <v>3.686899837763812</v>
       </c>
       <c r="E3">
-        <v>38.671868842954886</v>
+        <v>38.671868842954879</v>
       </c>
       <c r="F3">
-        <v>151.95799581723239</v>
+        <v>113.96849686292427</v>
       </c>
       <c r="G3">
-        <v>55.601747550941056</v>
+        <v>66.722097061129247</v>
       </c>
       <c r="H3">
-        <v>5.3880275545115515</v>
+        <v>3.8048987587382395</v>
       </c>
       <c r="I3">
-        <v>35.4573481015899</v>
+        <v>33.385530769214107</v>
       </c>
       <c r="J3">
         <v>97.126137383957371</v>
@@ -2852,7 +2852,7 @@
         <v>32.549285640722566</v>
       </c>
       <c r="Z3">
-        <v>17.610386892780816</v>
+        <v>17.61038689278082</v>
       </c>
       <c r="AA3">
         <v>1.1471318418426688</v>
@@ -2861,25 +2861,25 @@
         <v>1.2915581285429063</v>
       </c>
       <c r="AC3">
-        <v>0.28886137042417587</v>
+        <v>0.28864532563333767</v>
       </c>
       <c r="AD3">
-        <v>0.601143887523368</v>
+        <v>0.60185334122656953</v>
       </c>
       <c r="AE3">
-        <v>95.580806260451013</v>
+        <v>46.491132161346023</v>
       </c>
       <c r="AF3">
-        <v>21.523392484953639</v>
+        <v>32.612336241707617</v>
       </c>
       <c r="AG3">
-        <v>44977.189918339063</v>
+        <v>33732.891798840683</v>
       </c>
       <c r="AH3">
-        <v>4817.7987408611307</v>
+        <v>5781.359236787066</v>
       </c>
       <c r="AI3">
-        <v>4817.7987408611307</v>
+        <v>5781.359236787066</v>
       </c>
       <c r="AJ3">
         <v>25.224823161491528</v>
@@ -2894,136 +2894,136 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-7.3301527292269313</v>
+        <v>-7.3301485429871915</v>
       </c>
       <c r="AO3">
-        <v>-3.976142079634112</v>
+        <v>-3.9761575560966826</v>
       </c>
       <c r="AP3">
-        <v>-1.1101905415015743</v>
+        <v>-1.1102181812487677</v>
       </c>
       <c r="AQ3">
-        <v>-1.2499102442633705</v>
+        <v>-1.2498610103715067</v>
       </c>
       <c r="AR3">
-        <v>1139.9779722771816</v>
+        <v>854.34624584642256</v>
       </c>
       <c r="AS3">
-        <v>225.90787190205182</v>
+        <v>271.40618234765185</v>
       </c>
       <c r="AT3">
-        <v>-0.98643619018202644</v>
+        <v>-1.0187783603519287</v>
       </c>
       <c r="AU3">
-        <v>-0.13518820829713973</v>
+        <v>-0.24191574116330272</v>
       </c>
       <c r="AV3">
-        <v>-0.47229347200482547</v>
+        <v>-0.48777850387383609</v>
       </c>
       <c r="AW3">
-        <v>0.13819438790735958</v>
+        <v>0.24729522046580138</v>
       </c>
       <c r="AX3">
-        <v>0.81671007444837262</v>
+        <v>0.84348745393848312</v>
       </c>
       <c r="AY3">
-        <v>0.30699822119147052</v>
+        <v>0.54936523792157888</v>
       </c>
       <c r="AZ3">
-        <v>-1.9513312125045885</v>
+        <v>-2.0153092850457224</v>
       </c>
       <c r="BA3">
-        <v>0.33678326770626849</v>
+        <v>0.60266479484279623</v>
       </c>
       <c r="BB3">
-        <v>-0.73032245394678574</v>
+        <v>-1.0340149371089473</v>
       </c>
       <c r="BC3">
-        <v>-0.402869775632185</v>
+        <v>-0.56925152628480713</v>
       </c>
       <c r="BD3">
-        <v>-0.15790598241893242</v>
+        <v>-0.16308271319743103</v>
       </c>
       <c r="BE3">
-        <v>-0.046470710939808237</v>
+        <v>-0.0831578736746041</v>
       </c>
       <c r="BF3">
-        <v>-0.13851669616343965</v>
+        <v>-0.19088597157217074</v>
       </c>
       <c r="BG3">
-        <v>-0.20570647029049438</v>
+        <v>-0.30639638697723115</v>
       </c>
       <c r="BH3">
-        <v>64.504954009713572</v>
+        <v>64.507461242136259</v>
       </c>
       <c r="BI3">
-        <v>41.295315680632612</v>
+        <v>40.612133793050219</v>
       </c>
       <c r="BJ3">
-        <v>-1.4097764545291707</v>
+        <v>-1.4560699076659864</v>
       </c>
       <c r="BK3">
-        <v>0.4529101495044614</v>
+        <v>0.80933714738855667</v>
       </c>
       <c r="BL3">
-        <v>-1.5770983466021562</v>
+        <v>-1.628742773838979</v>
       </c>
       <c r="BM3">
-        <v>0.050430880395701844</v>
+        <v>0.099901959122414119</v>
       </c>
       <c r="BN3">
-        <v>0.1362099110439248</v>
+        <v>0.0883301794697377</v>
       </c>
       <c r="BO3">
-        <v>0.028501595015576982</v>
+        <v>0.039895053175310342</v>
       </c>
       <c r="BP3">
-        <v>-1.5456207507940589</v>
+        <v>-0.82875507310744911</v>
       </c>
       <c r="BQ3">
-        <v>1.7806590102337976</v>
+        <v>1.4199201121317171</v>
       </c>
       <c r="BR3">
-        <v>38.791296111820834</v>
+        <v>39.513234790106829</v>
       </c>
       <c r="BS3">
-        <v>-1.4422585075995176</v>
+        <v>-1.4071363195198061</v>
       </c>
       <c r="BT3">
-        <v>-0.048620284148437658</v>
+        <v>-0.43611287429311835</v>
       </c>
       <c r="BU3">
-        <v>1.354453403602387</v>
+        <v>1.548778940498257</v>
       </c>
       <c r="BV3">
-        <v>21.367207109033021</v>
+        <v>21.366884189946514</v>
       </c>
       <c r="BW3">
-        <v>-1.5264580775408583</v>
+        <v>-1.5309715595708855</v>
       </c>
       <c r="BX3">
-        <v>-26.318163319371571</v>
+        <v>-44.510925049534862</v>
       </c>
       <c r="BY3">
-        <v>28.501856667642883</v>
+        <v>38.443430979054249</v>
       </c>
       <c r="BZ3">
-        <v>22.632896472783088</v>
+        <v>45.978368431505537</v>
       </c>
       <c r="CA3">
-        <v>-32.344453127822604</v>
+        <v>-38.363190941726018</v>
       </c>
       <c r="CB3">
-        <v>58.090409721274881</v>
+        <v>79.3641287597623</v>
       </c>
       <c r="CC3">
-        <v>28.502598980703119</v>
+        <v>38.444651958201682</v>
       </c>
       <c r="CD3">
-        <v>3.6150545504431197</v>
+        <v>2.646031693180638</v>
       </c>
       <c r="CE3">
-        <v>7.3677491705993052</v>
+        <v>5.4623982609679764</v>
       </c>
     </row>
     <row r="4" spans="1:83">
@@ -3031,28 +3031,28 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>435.74359794931456</v>
+        <v>443.14615453651362</v>
       </c>
       <c r="C4">
-        <v>163.2443505702883</v>
+        <v>110.01317881165521</v>
       </c>
       <c r="D4">
-        <v>6.7462500708430868</v>
+        <v>4.4977161651984243</v>
       </c>
       <c r="E4">
-        <v>41.326086000987495</v>
+        <v>40.8834306378748</v>
       </c>
       <c r="F4">
-        <v>173.53724208300113</v>
+        <v>130.15293156225084</v>
       </c>
       <c r="G4">
-        <v>89.890886510164236</v>
+        <v>107.86906381219706</v>
       </c>
       <c r="H4">
-        <v>6.59834708088809</v>
+        <v>4.6353807475335183</v>
       </c>
       <c r="I4">
-        <v>38.022657279134158</v>
+        <v>35.614877758757679</v>
       </c>
       <c r="J4">
         <v>126.70749296979982</v>
@@ -3100,10 +3100,10 @@
         <v>51.470815454060336</v>
       </c>
       <c r="Y4">
-        <v>34.783720175771847</v>
+        <v>34.783720175771855</v>
       </c>
       <c r="Z4">
-        <v>22.391464965209213</v>
+        <v>22.391464965209209</v>
       </c>
       <c r="AA4">
         <v>2.4313189838673996</v>
@@ -3112,25 +3112,25 @@
         <v>3.1498315145934139</v>
       </c>
       <c r="AC4">
-        <v>0.572438583166304</v>
+        <v>0.57200997572570866</v>
       </c>
       <c r="AD4">
-        <v>1.1492129892444749</v>
+        <v>1.150575043791177</v>
       </c>
       <c r="AE4">
-        <v>196.13046898130963</v>
+        <v>114.24211194277611</v>
       </c>
       <c r="AF4">
-        <v>115.51022125789082</v>
+        <v>156.33905922830087</v>
       </c>
       <c r="AG4">
-        <v>58662.798598892245</v>
+        <v>43997.095671784882</v>
       </c>
       <c r="AH4">
-        <v>12595.883374989089</v>
+        <v>15115.06719194062</v>
       </c>
       <c r="AI4">
-        <v>12595.883374989089</v>
+        <v>15115.06719194062</v>
       </c>
       <c r="AJ4">
         <v>26.956449982266708</v>
@@ -3145,136 +3145,136 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-7.8511702954378348</v>
+        <v>-7.8511526933615787</v>
       </c>
       <c r="AO4">
-        <v>-5.1008404786710368</v>
+        <v>-5.1009129386661627</v>
       </c>
       <c r="AP4">
-        <v>-2.35299716860912</v>
+        <v>-2.3530559000944469</v>
       </c>
       <c r="AQ4">
-        <v>-3.0481411302783696</v>
+        <v>-3.0480198705211485</v>
       </c>
       <c r="AR4">
-        <v>1391.3116858003177</v>
+        <v>1042.7070404902058</v>
       </c>
       <c r="AS4">
-        <v>464.43184133287156</v>
+        <v>557.96614834322838</v>
       </c>
       <c r="AT4">
-        <v>-0.888478917576636</v>
+        <v>-0.35181379957732561</v>
       </c>
       <c r="AU4">
-        <v>-0.58267210304332007</v>
+        <v>-0.06458188334223991</v>
       </c>
       <c r="AV4">
-        <v>-0.55407091912256667</v>
+        <v>-0.21939720958544587</v>
       </c>
       <c r="AW4">
-        <v>0.34933033084375187</v>
+        <v>0.038718879034406</v>
       </c>
       <c r="AX4">
-        <v>1.1336802812142974</v>
+        <v>0.44890695699089633</v>
       </c>
       <c r="AY4">
-        <v>0.92000649477055074</v>
+        <v>0.10197116321348471</v>
       </c>
       <c r="AZ4">
-        <v>-2.309522320221387</v>
+        <v>-0.91450883820846873</v>
       </c>
       <c r="BA4">
-        <v>1.7523116293338481</v>
+        <v>0.194221732315328</v>
       </c>
       <c r="BB4">
-        <v>-0.56623471336054632</v>
+        <v>-0.30982521524853468</v>
       </c>
       <c r="BC4">
-        <v>-0.38441699799403428</v>
+        <v>-0.20990186906839345</v>
       </c>
       <c r="BD4">
-        <v>-0.18069618694058434</v>
+        <v>-0.071550677653240247</v>
       </c>
       <c r="BE4">
-        <v>-0.2531447169624117</v>
+        <v>-0.028057644388363528</v>
       </c>
       <c r="BF4">
-        <v>-0.12987469938243443</v>
+        <v>-0.06862011559795575</v>
       </c>
       <c r="BG4">
-        <v>-0.54506322442473454</v>
+        <v>-0.0502855674518521</v>
       </c>
       <c r="BH4">
-        <v>57.851955925174451</v>
+        <v>56.762870092914888</v>
       </c>
       <c r="BI4">
-        <v>43.029393106279372</v>
+        <v>32.681124980383863</v>
       </c>
       <c r="BJ4">
-        <v>-1.3521760207375828</v>
+        <v>-0.51885538170525536</v>
       </c>
       <c r="BK4">
-        <v>1.8682591332721614</v>
+        <v>0.190700539731131</v>
       </c>
       <c r="BL4">
-        <v>-2.1887769042451963</v>
+        <v>-0.87671715169245057</v>
       </c>
       <c r="BM4">
-        <v>0.65315833276763191</v>
+        <v>0.10841357653418407</v>
       </c>
       <c r="BN4">
-        <v>0.31007656829078262</v>
+        <v>0.25138261359193065</v>
       </c>
       <c r="BO4">
-        <v>0.18369371062588247</v>
+        <v>0.33690448219768171</v>
       </c>
       <c r="BP4">
-        <v>-0.80561254884248867</v>
+        <v>-0.81296423267654594</v>
       </c>
       <c r="BQ4">
-        <v>2.1141410658427815</v>
+        <v>1.7535395294527385</v>
       </c>
       <c r="BR4">
-        <v>39.481907524467836</v>
+        <v>39.484862028340352</v>
       </c>
       <c r="BS4">
-        <v>-2.8835857990228568</v>
+        <v>-2.8428435472045033</v>
       </c>
       <c r="BT4">
-        <v>-0.02403242797190738</v>
+        <v>-0.014414665375272496</v>
       </c>
       <c r="BU4">
-        <v>1.6970408260157588</v>
+        <v>1.8911668581861469</v>
       </c>
       <c r="BV4">
-        <v>21.3192804564197</v>
+        <v>21.311179624462461</v>
       </c>
       <c r="BW4">
-        <v>-2.9739955315643245</v>
+        <v>-3.0314998952893442</v>
       </c>
       <c r="BX4">
-        <v>-14.605513483975463</v>
+        <v>-7.9802806002055977</v>
       </c>
       <c r="BY4">
-        <v>27.449137721011418</v>
+        <v>2.3069264087883816</v>
       </c>
       <c r="BZ4">
-        <v>21.353329028151794</v>
+        <v>13.698195058986999</v>
       </c>
       <c r="CA4">
-        <v>-49.206830973112446</v>
+        <v>-3.8506433055442235</v>
       </c>
       <c r="CB4">
-        <v>59.376128346335854</v>
+        <v>49.313120560845192</v>
       </c>
       <c r="CC4">
-        <v>27.454548904428794</v>
+        <v>2.3074743972272396</v>
       </c>
       <c r="CD4">
-        <v>3.5367748933559295</v>
+        <v>4.2585015430303308</v>
       </c>
       <c r="CE4">
-        <v>7.6490056613577844</v>
+        <v>91.0085937474951</v>
       </c>
     </row>
     <row r="5" spans="1:83">
@@ -3282,28 +3282,28 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>408.4214732278175</v>
+        <v>416.10101215926147</v>
       </c>
       <c r="C5">
-        <v>207.90056424220626</v>
+        <v>150.76704080036583</v>
       </c>
       <c r="D5">
-        <v>8.9683937465522128</v>
+        <v>5.9993975018123455</v>
       </c>
       <c r="E5">
-        <v>43.137899982339356</v>
+        <v>39.7925002040485</v>
       </c>
       <c r="F5">
-        <v>221.56851216319822</v>
+        <v>166.17638412239867</v>
       </c>
       <c r="G5">
-        <v>185.61849811915124</v>
+        <v>222.7421977429814</v>
       </c>
       <c r="H5">
-        <v>8.8333231312651375</v>
+        <v>6.1795667534168679</v>
       </c>
       <c r="I5">
-        <v>39.867231336368206</v>
+        <v>37.186792732625925</v>
       </c>
       <c r="J5">
         <v>165.28254301559932</v>
@@ -3354,34 +3354,34 @@
         <v>39.303724211746172</v>
       </c>
       <c r="Z5">
-        <v>32.176240822764605</v>
+        <v>32.176240822764619</v>
       </c>
       <c r="AA5">
         <v>2.3948521974388464</v>
       </c>
       <c r="AB5">
-        <v>4.0941574182803384</v>
+        <v>4.0941574182803393</v>
       </c>
       <c r="AC5">
-        <v>0.49914020720919217</v>
+        <v>0.49876661277290857</v>
       </c>
       <c r="AD5">
-        <v>1.0403731755062255</v>
+        <v>1.0416049389677955</v>
       </c>
       <c r="AE5">
-        <v>282.32792534288086</v>
+        <v>158.184492930943</v>
       </c>
       <c r="AF5">
-        <v>430.28694046082711</v>
+        <v>591.93582476774031</v>
       </c>
       <c r="AG5">
-        <v>95627.57320084564</v>
+        <v>71720.675838549723</v>
       </c>
       <c r="AH5">
-        <v>53704.259968536142</v>
+        <v>64445.1369205682</v>
       </c>
       <c r="AI5">
-        <v>53704.259968536142</v>
+        <v>64445.1369205682</v>
       </c>
       <c r="AJ5">
         <v>30.459331850556751</v>
@@ -3396,136 +3396,136 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>-8.8649195774396912</v>
+        <v>-8.8649044647117279</v>
       </c>
       <c r="AO5">
-        <v>-7.3136611510282989</v>
+        <v>-7.3137463260761617</v>
       </c>
       <c r="AP5">
-        <v>-2.3177131340547779</v>
+        <v>-2.3177709372967858</v>
       </c>
       <c r="AQ5">
-        <v>-3.962016856452597</v>
+        <v>-3.9618596240506512</v>
       </c>
       <c r="AR5">
-        <v>2007.1975569571061</v>
+        <v>1504.2771513692476</v>
       </c>
       <c r="AS5">
-        <v>1378.0788703220767</v>
+        <v>1655.6195785403675</v>
       </c>
       <c r="AT5">
-        <v>-0.79965302133193816</v>
+        <v>-0.34675219509084043</v>
       </c>
       <c r="AU5">
-        <v>-0.78572303365161478</v>
+        <v>-0.29981536810390569</v>
       </c>
       <c r="AV5">
-        <v>-0.48024618853712236</v>
+        <v>-0.20824834724176103</v>
       </c>
       <c r="AW5">
-        <v>0.501153193545012</v>
+        <v>0.19122950806322828</v>
       </c>
       <c r="AX5">
-        <v>1.2235947713990631</v>
+        <v>0.53058534335003626</v>
       </c>
       <c r="AY5">
-        <v>1.7064792575571262</v>
+        <v>0.65115655880469292</v>
       </c>
       <c r="AZ5">
-        <v>-2.6729239713688178</v>
+        <v>-1.1590555274077177</v>
       </c>
       <c r="BA5">
-        <v>3.124371839007805</v>
+        <v>1.1921945175161361</v>
       </c>
       <c r="BB5">
-        <v>-0.42609693340817206</v>
+        <v>-0.25697538782093243</v>
       </c>
       <c r="BC5">
-        <v>-0.27626083773461763</v>
+        <v>-0.16628380740825777</v>
       </c>
       <c r="BD5">
-        <v>-0.2141056579846887</v>
+        <v>-0.092842159004405081</v>
       </c>
       <c r="BE5">
-        <v>-0.541862802294673</v>
+        <v>-0.20676172441517335</v>
       </c>
       <c r="BF5">
-        <v>-0.1066689510669149</v>
+        <v>-0.061718785610681365</v>
       </c>
       <c r="BG5">
-        <v>-0.39320158952007728</v>
+        <v>-0.12488480270175306</v>
       </c>
       <c r="BH5">
-        <v>60.26390226320617</v>
+        <v>59.337287078123822</v>
       </c>
       <c r="BI5">
-        <v>45.707374428264906</v>
+        <v>45.282795186462806</v>
       </c>
       <c r="BJ5">
-        <v>-1.714041041474077</v>
+        <v>-0.72641178702778242</v>
       </c>
       <c r="BK5">
-        <v>3.4280450538791483</v>
+        <v>1.3053184231955233</v>
       </c>
       <c r="BL5">
-        <v>-2.388256692538647</v>
+        <v>-1.0475000896703364</v>
       </c>
       <c r="BM5">
-        <v>0.96035303583236642</v>
+        <v>0.37613354774103197</v>
       </c>
       <c r="BN5">
-        <v>0.23569516399254403</v>
+        <v>0.18222664845586756</v>
       </c>
       <c r="BO5">
-        <v>0.12860436938765649</v>
+        <v>0.15164625691948686</v>
       </c>
       <c r="BP5">
-        <v>-0.81214068818689933</v>
+        <v>-0.81832223255003433</v>
       </c>
       <c r="BQ5">
-        <v>2.0277268302993829</v>
+        <v>1.6671818962907412</v>
       </c>
       <c r="BR5">
-        <v>39.492951700118709</v>
+        <v>39.495274161539889</v>
       </c>
       <c r="BS5">
-        <v>-2.4899908674384474</v>
+        <v>-2.4528773741539123</v>
       </c>
       <c r="BT5">
-        <v>-0.030256749284818051</v>
+        <v>-0.025523493358071195</v>
       </c>
       <c r="BU5">
-        <v>1.6298740081228644</v>
+        <v>1.8239773729948969</v>
       </c>
       <c r="BV5">
-        <v>21.33252690676925</v>
+        <v>21.331391063211278</v>
       </c>
       <c r="BW5">
-        <v>-2.6765382689505612</v>
+        <v>-2.6855756629707215</v>
       </c>
       <c r="BX5">
-        <v>-12.330815029587372</v>
+        <v>-7.667952469334268</v>
       </c>
       <c r="BY5">
-        <v>12.985554096835775</v>
+        <v>4.0223269958341179</v>
       </c>
       <c r="BZ5">
-        <v>16.103302470002049</v>
+        <v>11.840895599154429</v>
       </c>
       <c r="CA5">
-        <v>-21.705136738122675</v>
+        <v>-6.0466482115518119</v>
       </c>
       <c r="CB5">
-        <v>55.970635451414672</v>
+        <v>49.027727179287929</v>
       </c>
       <c r="CC5">
-        <v>12.991505790009466</v>
+        <v>4.0242652342212448</v>
       </c>
       <c r="CD5">
-        <v>3.7519674076648739</v>
+        <v>4.2832905394952876</v>
       </c>
       <c r="CE5">
-        <v>16.1644079904495</v>
+        <v>52.183439156598759</v>
       </c>
     </row>
   </sheetData>
@@ -4377,10 +4377,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>440.07443020668313</v>
+        <v>447.55974118793</v>
       </c>
       <c r="C3">
-        <v>143.00704677873924</v>
+        <v>95.338031185826168</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -4389,10 +4389,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>143.00704677873924</v>
+        <v>95.338031185826168</v>
       </c>
       <c r="G3">
-        <v>91.467560427874034</v>
+        <v>117.60114912155233</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -4446,37 +4446,37 @@
         <v>37.922323195539839</v>
       </c>
       <c r="Y3">
-        <v>36.460932396303264</v>
+        <v>36.460932396303257</v>
       </c>
       <c r="Z3">
-        <v>19.08948476405914</v>
+        <v>19.089484764059137</v>
       </c>
       <c r="AA3">
-        <v>0.76744655432468711</v>
+        <v>0.767446554324687</v>
       </c>
       <c r="AB3">
         <v>1.3813926663976253</v>
       </c>
       <c r="AC3">
-        <v>0.17242114537246006</v>
+        <v>0.17232904763350362</v>
       </c>
       <c r="AD3">
-        <v>0.59458778435515369</v>
+        <v>0.59663861029328635</v>
       </c>
       <c r="AE3">
-        <v>58.9470189258858</v>
+        <v>20.3960297978814</v>
       </c>
       <c r="AF3">
-        <v>65.007527966928961</v>
+        <v>124.45570987017457</v>
       </c>
       <c r="AG3">
-        <v>53111.8868523204</v>
+        <v>35407.924397127885</v>
       </c>
       <c r="AH3">
-        <v>9314.2712429899311</v>
+        <v>11975.496015531709</v>
       </c>
       <c r="AI3">
-        <v>9314.2712429899311</v>
+        <v>11975.496015531709</v>
       </c>
       <c r="AJ3">
         <v>28.256244458071322</v>
@@ -4491,136 +4491,136 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-8.2069602737230287</v>
+        <v>-8.2069590798053476</v>
       </c>
       <c r="AO3">
-        <v>-4.3097500537499238</v>
+        <v>-4.3097978978469991</v>
       </c>
       <c r="AP3">
-        <v>-0.742752612277877</v>
+        <v>-0.74276580421690552</v>
       </c>
       <c r="AQ3">
-        <v>-1.3367409533919472</v>
+        <v>-1.3365866907859907</v>
       </c>
       <c r="AR3">
-        <v>1200.845087427768</v>
+        <v>800.13649294105869</v>
       </c>
       <c r="AS3">
-        <v>403.93534011285863</v>
+        <v>521.105965064599</v>
       </c>
       <c r="AT3">
-        <v>-1.1989945576635537</v>
+        <v>-1.2383058546361294</v>
       </c>
       <c r="AU3">
-        <v>-0.1201953525636778</v>
+        <v>-0.21508642037710762</v>
       </c>
       <c r="AV3">
-        <v>-0.47229347200482547</v>
+        <v>-0.48777850387383614</v>
       </c>
       <c r="AW3">
-        <v>0.13955972214128534</v>
+        <v>0.24973845014756321</v>
       </c>
       <c r="AX3">
         <v>0</v>
       </c>
       <c r="AY3">
-        <v>1.0873817847998957</v>
+        <v>1.9458410885892865</v>
       </c>
       <c r="AZ3">
         <v>0</v>
       </c>
       <c r="BA3">
-        <v>1.1378986586504882</v>
+        <v>2.036239704953505</v>
       </c>
       <c r="BB3">
-        <v>-1.4481473106859937</v>
+        <v>-2.1164478993961939</v>
       </c>
       <c r="BC3">
-        <v>-0.78011572238571159</v>
+        <v>-1.1324895855817485</v>
       </c>
       <c r="BD3">
         <v>0</v>
       </c>
       <c r="BE3">
-        <v>-0.090012591526002647</v>
+        <v>-0.16107407572556909</v>
       </c>
       <c r="BF3">
         <v>0</v>
       </c>
       <c r="BG3">
-        <v>-0.22283910959821771</v>
+        <v>-0.30910042587135139</v>
       </c>
       <c r="BH3">
-        <v>69.160070220701</v>
+        <v>69.176413028954784</v>
       </c>
       <c r="BI3">
-        <v>38.139888143785285</v>
+        <v>37.437271104952387</v>
       </c>
       <c r="BJ3">
         <v>0</v>
       </c>
       <c r="BK3">
-        <v>1.5579790172431225</v>
+        <v>2.7828502864672062</v>
       </c>
       <c r="BL3">
         <v>0</v>
       </c>
       <c r="BM3">
-        <v>0.22341415600480952</v>
+        <v>0.43395156547806768</v>
       </c>
       <c r="BN3">
         <v>90</v>
       </c>
       <c r="BO3">
-        <v>0.05734378311807295</v>
+        <v>0.092852795782882525</v>
       </c>
       <c r="BP3">
-        <v>-0.65772075266487007</v>
+        <v>-0.65777936373374113</v>
       </c>
       <c r="BQ3">
-        <v>36.463076787800766</v>
+        <v>36.463075730527542</v>
       </c>
       <c r="BR3">
-        <v>-0.90066892298733769</v>
+        <v>-0.900597765113804</v>
       </c>
       <c r="BS3">
-        <v>-44.2686846809928</v>
+        <v>-44.268686128678738</v>
       </c>
       <c r="BT3">
-        <v>-0.4701037743402276</v>
+        <v>-0.46378961439048383</v>
       </c>
       <c r="BU3">
-        <v>1.8845779942894334</v>
+        <v>2.3068931140383966</v>
       </c>
       <c r="BV3">
-        <v>23.161407393374205</v>
+        <v>-14.041138066770371</v>
       </c>
       <c r="BW3">
-        <v>-1.6450321215489803</v>
+        <v>-1.8955133687332133</v>
       </c>
       <c r="BX3">
         <v>0</v>
       </c>
       <c r="BY3">
-        <v>45.177321596449538</v>
+        <v>51.599318294385796</v>
       </c>
       <c r="BZ3">
         <v>0</v>
       </c>
       <c r="CA3">
-        <v>-39.980612105908058</v>
+        <v>-41.875189418245931</v>
       </c>
       <c r="CB3">
         <v>0</v>
       </c>
       <c r="CC3">
-        <v>45.177871174921385</v>
+        <v>51.600244103285114</v>
       </c>
       <c r="CD3">
         <v>1E+307</v>
       </c>
       <c r="CE3">
-        <v>4.64829339095935</v>
+        <v>4.0697481891685543</v>
       </c>
     </row>
     <row r="4" spans="1:83">
@@ -4628,28 +4628,28 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>435.74359794931456</v>
+        <v>443.14615453651362</v>
       </c>
       <c r="C4">
-        <v>163.2443505702883</v>
+        <v>108.82956704685887</v>
       </c>
       <c r="D4">
-        <v>0.57377880643943746</v>
+        <v>0.38251920429295833</v>
       </c>
       <c r="E4">
         <v>3.5148463296583414</v>
       </c>
       <c r="F4">
-        <v>163.2443505702883</v>
+        <v>108.82956704685886</v>
       </c>
       <c r="G4">
-        <v>147.83001946415376</v>
+        <v>190.06716788248338</v>
       </c>
       <c r="H4">
-        <v>0.58109964567733086</v>
+        <v>0.38595005695591861</v>
       </c>
       <c r="I4">
-        <v>3.5596922260848847</v>
+        <v>3.5463713348206163</v>
       </c>
       <c r="J4">
         <v>126.98694743576179</v>
@@ -4700,34 +4700,34 @@
         <v>38.955441574532315</v>
       </c>
       <c r="Z4">
-        <v>24.268446449383816</v>
+        <v>24.268446449383809</v>
       </c>
       <c r="AA4">
-        <v>1.3915176549378143</v>
+        <v>1.3915176549378139</v>
       </c>
       <c r="AB4">
-        <v>3.4600516362771381</v>
+        <v>3.4602749379742446</v>
       </c>
       <c r="AC4">
-        <v>0.2925566389668916</v>
+        <v>0.29240042898802476</v>
       </c>
       <c r="AD4">
-        <v>1.1674327507274593</v>
+        <v>1.1695525618683607</v>
       </c>
       <c r="AE4">
-        <v>96.1726402350547</v>
+        <v>39.500516904168272</v>
       </c>
       <c r="AF4">
-        <v>289.61198883964073</v>
+        <v>478.84267547875788</v>
       </c>
       <c r="AG4">
-        <v>69208.678020488514</v>
+        <v>46139.118038905479</v>
       </c>
       <c r="AH4">
-        <v>24337.259991042236</v>
+        <v>31290.765128618685</v>
       </c>
       <c r="AI4">
-        <v>24337.259991042236</v>
+        <v>31290.765128618685</v>
       </c>
       <c r="AJ4">
         <v>30.189422150205413</v>
@@ -4742,136 +4742,136 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-8.7730103155259727</v>
+        <v>-8.7730066437711454</v>
       </c>
       <c r="AO4">
-        <v>-5.5304134955891362</v>
+        <v>-5.5305419204495685</v>
       </c>
       <c r="AP4">
-        <v>-1.3467397429923422</v>
+        <v>-1.3467636615336522</v>
       </c>
       <c r="AQ4">
-        <v>-3.348069215476583</v>
+        <v>-3.3480878558716047</v>
       </c>
       <c r="AR4">
-        <v>1464.5836296447237</v>
+        <v>975.86890573556263</v>
       </c>
       <c r="AS4">
-        <v>830.04240621893234</v>
+        <v>1070.7855460308531</v>
       </c>
       <c r="AT4">
-        <v>-1.2247142692195434</v>
+        <v>-0.48495397237552385</v>
       </c>
       <c r="AU4">
-        <v>-0.5226075805833329</v>
+        <v>-0.05792448553263542</v>
       </c>
       <c r="AV4">
-        <v>-0.55660876209823451</v>
+        <v>-0.22040212727379754</v>
       </c>
       <c r="AW4">
-        <v>0.35805489877027769</v>
+        <v>0.039685887794735211</v>
       </c>
       <c r="AX4">
-        <v>0.0072761481867066368</v>
+        <v>0.002881159349098601</v>
       </c>
       <c r="AY4">
-        <v>3.0074337026455793</v>
+        <v>0.333336247830175</v>
       </c>
       <c r="AZ4">
-        <v>-0.016271291071232388</v>
+        <v>-0.0064429944510249063</v>
       </c>
       <c r="BA4">
-        <v>5.4478549793682571</v>
+        <v>0.60382629081667871</v>
       </c>
       <c r="BB4">
-        <v>-1.2037607471595737</v>
+        <v>-0.680184216605784</v>
       </c>
       <c r="BC4">
-        <v>-0.77503701146690018</v>
+        <v>-0.43473639300723821</v>
       </c>
       <c r="BD4">
-        <v>-0.016715518021894995</v>
+        <v>-0.0066188177241276094</v>
       </c>
       <c r="BE4">
-        <v>-0.46725451827857706</v>
+        <v>-0.051789019013886009</v>
       </c>
       <c r="BF4">
-        <v>-0.011413153666035321</v>
+        <v>-0.0067824865463242383</v>
       </c>
       <c r="BG4">
-        <v>-0.56292848989131494</v>
+        <v>-0.048365444608264994</v>
       </c>
       <c r="BH4">
-        <v>66.6514233586956</v>
+        <v>64.992859055657348</v>
       </c>
       <c r="BI4">
-        <v>40.18407743937383</v>
+        <v>30.581622678192684</v>
       </c>
       <c r="BJ4">
-        <v>-0.012055133976229222</v>
+        <v>-0.0046210406406382333</v>
       </c>
       <c r="BK4">
-        <v>5.812808665249328</v>
+        <v>0.59417679814830571</v>
       </c>
       <c r="BL4">
-        <v>-0.013129013305456162</v>
+        <v>-0.0053347202446244364</v>
       </c>
       <c r="BM4">
-        <v>2.2214942658576313</v>
+        <v>0.35024730711478114</v>
       </c>
       <c r="BN4">
-        <v>0.086710827978065452</v>
+        <v>0.056627559223427382</v>
       </c>
       <c r="BO4">
-        <v>0.26056954904723323</v>
+        <v>0.51682871471937308</v>
       </c>
       <c r="BP4">
-        <v>-0.928254409976568</v>
+        <v>-0.12421320613887013</v>
       </c>
       <c r="BQ4">
-        <v>1.595674029821301</v>
+        <v>1.1925068891779702</v>
       </c>
       <c r="BR4">
-        <v>44.261603499044647</v>
+        <v>44.262439369604074</v>
       </c>
       <c r="BS4">
-        <v>-1.5954329074598734</v>
+        <v>-1.5720723650550248</v>
       </c>
       <c r="BT4">
-        <v>-0.012253725731403591</v>
+        <v>-0.41242540375504727</v>
       </c>
       <c r="BU4">
-        <v>2.2706067981352978</v>
+        <v>2.6936159347035429</v>
       </c>
       <c r="BV4">
-        <v>23.103600860749864</v>
+        <v>23.088486253898886</v>
       </c>
       <c r="BW4">
-        <v>-3.2984496248856345</v>
+        <v>-3.4027784688058333</v>
       </c>
       <c r="BX4">
-        <v>-0.20019206455872463</v>
+        <v>-0.13952197417240175</v>
       </c>
       <c r="BY4">
-        <v>45.574518029123588</v>
+        <v>3.3470171017903</v>
       </c>
       <c r="BZ4">
-        <v>0.20838225603107069</v>
+        <v>0.18902951178968561</v>
       </c>
       <c r="CA4">
-        <v>-68.312142145434</v>
+        <v>-4.4808088676945221</v>
       </c>
       <c r="CB4">
-        <v>3.7680917667766569</v>
+        <v>3.7354070041938816</v>
       </c>
       <c r="CC4">
-        <v>45.577994493742722</v>
+        <v>3.3473665314555703</v>
       </c>
       <c r="CD4">
-        <v>55.731126787190888</v>
+        <v>56.218773419931239</v>
       </c>
       <c r="CE4">
-        <v>4.607486624468093</v>
+        <v>62.735884471152765</v>
       </c>
     </row>
     <row r="5" spans="1:83">
@@ -4879,28 +4879,28 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>408.4214732278175</v>
+        <v>416.10101215926147</v>
       </c>
       <c r="C5">
-        <v>207.90056424220626</v>
+        <v>138.60037616147085</v>
       </c>
       <c r="D5">
-        <v>1.3263861420993071</v>
+        <v>0.884257428066205</v>
       </c>
       <c r="E5">
-        <v>6.3799064083061063</v>
+        <v>6.3799064083061072</v>
       </c>
       <c r="F5">
-        <v>207.90056424220626</v>
+        <v>138.60037616147085</v>
       </c>
       <c r="G5">
-        <v>304.71985697312419</v>
+        <v>391.78267325115968</v>
       </c>
       <c r="H5">
-        <v>1.3576192148630719</v>
+        <v>0.89879528642217954</v>
       </c>
       <c r="I5">
-        <v>6.5301372308034322</v>
+        <v>6.4847968765616759</v>
       </c>
       <c r="J5">
         <v>165.79407761584392</v>
@@ -4957,28 +4957,28 @@
         <v>1.3199160605108644</v>
       </c>
       <c r="AB5">
-        <v>4.5704270373995275</v>
+        <v>4.57072246503231</v>
       </c>
       <c r="AC5">
-        <v>0.24592069709707615</v>
+        <v>0.24578940314556474</v>
       </c>
       <c r="AD5">
-        <v>1.0748617877481994</v>
+        <v>1.0768116430620662</v>
       </c>
       <c r="AE5">
-        <v>141.85717261157575</v>
+        <v>54.6477556201993</v>
       </c>
       <c r="AF5">
-        <v>1126.817236733468</v>
+        <v>1901.3978037337504</v>
       </c>
       <c r="AG5">
-        <v>112251.52558896747</v>
+        <v>74834.349657540588</v>
       </c>
       <c r="AH5">
-        <v>103400.09585395634</v>
+        <v>132942.98854160856</v>
       </c>
       <c r="AI5">
-        <v>103400.09585395634</v>
+        <v>132942.98854160856</v>
       </c>
       <c r="AJ5">
         <v>34.069326956572112</v>
@@ -4993,136 +4993,136 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>-9.8981908109314887</v>
+        <v>-9.8981878836283155</v>
       </c>
       <c r="AO5">
-        <v>-7.9248844164709444</v>
+        <v>-7.9250404691407086</v>
       </c>
       <c r="AP5">
-        <v>-1.2774436769117923</v>
+        <v>-1.2774663587289044</v>
       </c>
       <c r="AQ5">
-        <v>-4.422544095839</v>
+        <v>-4.4225697738650647</v>
       </c>
       <c r="AR5">
-        <v>2104.9299866067313</v>
+        <v>1402.5389435628135</v>
       </c>
       <c r="AS5">
-        <v>2456.4277071614119</v>
+        <v>3168.8990899315422</v>
       </c>
       <c r="AT5">
-        <v>-1.13803725517239</v>
+        <v>-0.49348518144643466</v>
       </c>
       <c r="AU5">
-        <v>-0.70077979036868321</v>
+        <v>-0.26740281474594485</v>
       </c>
       <c r="AV5">
-        <v>-0.48756594061066955</v>
+        <v>-0.21142239902586557</v>
       </c>
       <c r="AW5">
-        <v>0.51511607430432882</v>
+        <v>0.19655744940559913</v>
       </c>
       <c r="AX5">
-        <v>0.023497924463031512</v>
+        <v>0.010189365475119859</v>
       </c>
       <c r="AY5">
-        <v>5.1598539259393021</v>
+        <v>1.9688916296347339</v>
       </c>
       <c r="AZ5">
-        <v>-0.056645200225527791</v>
+        <v>-0.024562962929653639</v>
       </c>
       <c r="BA5">
-        <v>8.9561448442219742</v>
+        <v>3.4174763221373321</v>
       </c>
       <c r="BB5">
-        <v>-0.9379861147502192</v>
+        <v>-0.58380787629991515</v>
       </c>
       <c r="BC5">
-        <v>-0.57669617623711489</v>
+        <v>-0.35632442940146514</v>
       </c>
       <c r="BD5">
-        <v>-0.03365747735652394</v>
+        <v>-0.014594657503388526</v>
       </c>
       <c r="BE5">
-        <v>-0.96866967359916833</v>
+        <v>-0.36962219299138621</v>
       </c>
       <c r="BF5">
-        <v>-0.015989832237024538</v>
+        <v>-0.010405883965199782</v>
       </c>
       <c r="BG5">
-        <v>-0.39434080261150428</v>
+        <v>-0.11664056901205117</v>
       </c>
       <c r="BH5">
-        <v>68.804169647639213</v>
+        <v>67.410696256449839</v>
       </c>
       <c r="BI5">
-        <v>42.300571144297457</v>
+        <v>42.161885291480438</v>
       </c>
       <c r="BJ5">
-        <v>-0.044317326482410054</v>
+        <v>-0.018764570849655451</v>
       </c>
       <c r="BK5">
-        <v>9.8440173778672939</v>
+        <v>3.7533479964795395</v>
       </c>
       <c r="BL5">
-        <v>-0.042388745394407991</v>
+        <v>-0.018842855343534439</v>
       </c>
       <c r="BM5">
-        <v>3.151498829440019</v>
+        <v>1.2116342182928175</v>
       </c>
       <c r="BN5">
-        <v>0.069256171197000616</v>
+        <v>0.042014768369097365</v>
       </c>
       <c r="BO5">
-        <v>0.19989327764299514</v>
+        <v>0.26453296182479968</v>
       </c>
       <c r="BP5">
-        <v>-0.93037181138125769</v>
+        <v>-0.12579753283121398</v>
       </c>
       <c r="BQ5">
-        <v>1.5340859518152079</v>
+        <v>1.1306324106086891</v>
       </c>
       <c r="BR5">
-        <v>44.264503008451996</v>
+        <v>44.2651372820476</v>
       </c>
       <c r="BS5">
-        <v>-1.3382177198294232</v>
+        <v>-1.3170704811815919</v>
       </c>
       <c r="BT5">
-        <v>-0.019697629567867667</v>
+        <v>-0.43005405251186785</v>
       </c>
       <c r="BU5">
-        <v>2.2089618893509884</v>
+        <v>2.630643991732379</v>
       </c>
       <c r="BV5">
-        <v>23.117182126895241</v>
+        <v>23.113653950082266</v>
       </c>
       <c r="BW5">
-        <v>-3.0190638250014028</v>
+        <v>-3.0460905379026593</v>
       </c>
       <c r="BX5">
-        <v>-0.47961217161454889</v>
+        <v>-0.38826046386586266</v>
       </c>
       <c r="BY5">
-        <v>19.298369789230847</v>
+        <v>5.1967951360952869</v>
       </c>
       <c r="BZ5">
-        <v>0.43478531376220597</v>
+        <v>0.46339231737834718</v>
       </c>
       <c r="CA5">
-        <v>-27.079503312670312</v>
+        <v>-6.2236210900752846</v>
       </c>
       <c r="CB5">
-        <v>6.9649408989978978</v>
+        <v>6.9481969860681128</v>
       </c>
       <c r="CC5">
-        <v>19.302398327423</v>
+        <v>5.1981039532586388</v>
       </c>
       <c r="CD5">
-        <v>30.151009613048458</v>
+        <v>30.22366815751953</v>
       </c>
       <c r="CE5">
-        <v>10.879477070041194</v>
+        <v>40.399345970823283</v>
       </c>
     </row>
   </sheetData>
